--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T06:29:04+00:00</t>
+    <t>2026-04-24T01:18:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
